--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T20:38:51+00:00</t>
+    <t>2026-07-29T12:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T12:58:51+00:00</t>
+    <t>2026-08-03T13:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:35:26+00:00</t>
+    <t>2026-08-11T08:10:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:10:28+00:00</t>
+    <t>2026-08-11T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:02+00:00</t>
+    <t>2026-08-28T09:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
